--- a/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260125_201254.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260125_201254.xlsx
@@ -5544,7 +5544,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5614,7 +5614,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5824,7 +5824,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260125_201254.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260125_201254.xlsx
@@ -5544,7 +5544,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5614,7 +5614,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5824,7 +5824,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
